--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488201_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488201_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7761</v>
+        <v>5.2875</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0238</v>
+        <v>4.7075</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7523</v>
+        <v>0.58</v>
       </c>
       <c r="G2" t="n">
         <v>2.5818</v>
@@ -610,13 +610,13 @@
         <v>2.4087</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9366</v>
+        <v>2.4479</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3874</v>
+        <v>2.0711</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5491</v>
+        <v>0.3768</v>
       </c>
       <c r="V2" t="n">
         <v>0.6283</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3182</v>
+        <v>4.1771</v>
       </c>
       <c r="E3" t="n">
-        <v>4.64</v>
+        <v>4.4989</v>
       </c>
       <c r="F3" t="n">
         <v>-0.3218</v>
@@ -688,10 +688,10 @@
         <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5793</v>
+        <v>1.4382</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3443</v>
+        <v>1.2031</v>
       </c>
       <c r="U3" t="n">
         <v>0.235</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRIGUEZ</t>
+          <t>A. DOBLADO GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3895</v>
+        <v>2.3875</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8167</v>
+        <v>3.5489</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5728</v>
+        <v>-1.1614</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.0098</v>
+        <v>-0.8171</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.3295</v>
+        <v>4.5914</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3197</v>
+        <v>-5.4085</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4367</v>
+        <v>1.7807</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8904</v>
+        <v>6.3293</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3271</v>
+        <v>-4.5487</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4465</v>
+        <v>-2.5978</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4391</v>
+        <v>-1.738</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0074</v>
+        <v>-0.8598</v>
       </c>
       <c r="P4" t="n">
         <v>0.1853</v>
@@ -766,28 +766,28 @@
         <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2702</v>
+        <v>0.8161</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2896</v>
+        <v>1.1034</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9806</v>
+        <v>-0.2873</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9439</v>
+        <v>2.2033</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9433</v>
+        <v>2.5177</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0005</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DOBLADO GARCIA</t>
+          <t>M. RAMOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1549</v>
+        <v>2.1963</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8087</v>
+        <v>1.1652</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6538</v>
+        <v>1.0311</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8171</v>
+        <v>-1.0098</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5914</v>
+        <v>-2.3295</v>
       </c>
       <c r="I5" t="n">
-        <v>-5.4085</v>
+        <v>1.3197</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7807</v>
+        <v>0.4367</v>
       </c>
       <c r="K5" t="n">
-        <v>6.3293</v>
+        <v>-0.8904</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.5487</v>
+        <v>1.3271</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5978</v>
+        <v>-1.4465</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.738</v>
+        <v>-1.4391</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8598</v>
+        <v>-0.0074</v>
       </c>
       <c r="P5" t="n">
         <v>0.1853</v>
@@ -844,28 +844,28 @@
         <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4166</v>
+        <v>2.077</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3631</v>
+        <v>1.6381</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7796999999999999</v>
+        <v>0.4389</v>
       </c>
       <c r="V5" t="n">
-        <v>2.2033</v>
+        <v>0.9439</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5177</v>
+        <v>0.9433</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3144</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. VIOQUE LOMBARDO</t>
+          <t>J. VIOQUE LOMBARDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2126</v>
+        <v>-0.2741</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0039</v>
+        <v>-0.2418</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2165</v>
+        <v>-0.0323</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9606</v>
+        <v>-1.4092</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9947</v>
+        <v>-1.2326</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0341</v>
+        <v>-0.1766</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1871</v>
+        <v>-0.5884</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1456</v>
+        <v>-0.5884</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0415</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1477</v>
+        <v>-0.8207</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1403</v>
+        <v>-0.6441</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0074</v>
+        <v>-0.1766</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.297</v>
+        <v>0.9264</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1922</v>
+        <v>0.2086</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3553</v>
+        <v>0.3466</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8369</v>
+        <v>-0.138</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8883</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VIOQUE LOMBARDO</t>
+          <t>I. VIOQUE LOMBARDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8376</v>
+        <v>-0.9916</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7314000000000001</v>
+        <v>0.4711</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1062</v>
+        <v>-1.4627</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4092</v>
+        <v>-0.9606</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2326</v>
+        <v>-0.9947</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1766</v>
+        <v>0.0341</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5884</v>
+        <v>0.1871</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5884</v>
+        <v>0.1456</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0415</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8207</v>
+        <v>-1.1477</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6441</v>
+        <v>-1.1403</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1766</v>
+        <v>-0.0074</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9264</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9264</v>
+        <v>1.297</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3549</v>
+        <v>2.4131</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.143</v>
+        <v>1.8224</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2119</v>
+        <v>0.5907</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.8883</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3066</v>
+        <v>-2.1841</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1212</v>
+        <v>-0.0233</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1854</v>
+        <v>-2.1608</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3989</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2783</v>
+        <v>-0.1558</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1641</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1142</v>
+        <v>-0.0895</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6294</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9421</v>
+        <v>-2.8195</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3861</v>
+        <v>-1.2881</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.556</v>
+        <v>-1.5314</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0518</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2783</v>
+        <v>-0.1558</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1641</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1142</v>
+        <v>-0.0895</v>
       </c>
       <c r="V9" t="n">
         <v>0.3144</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3891</v>
+        <v>-2.9968</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9711</v>
+        <v>-1.6773</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.418</v>
+        <v>-1.3195</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3622</v>
@@ -1234,13 +1234,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4143</v>
+        <v>-0.0221</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2736</v>
+        <v>0.0202</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1408</v>
+        <v>-0.0423</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3155</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5306</v>
+        <v>-4.0885</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2685</v>
+        <v>-2.0726</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2621</v>
+        <v>-2.0159</v>
       </c>
       <c r="G11" t="n">
         <v>-5.2469</v>
@@ -1312,13 +1312,13 @@
         <v>1.297</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3457</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5609</v>
+        <v>0.7567</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2151</v>
+        <v>0.0311</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4201000000000006</v>
+        <v>0.6938000000000013</v>
       </c>
       <c r="E12" t="n">
-        <v>8.814799999999998</v>
+        <v>9.088499999999998</v>
       </c>
       <c r="F12" t="n">
         <v>-8.3947</v>
@@ -1390,13 +1390,13 @@
         <v>12.0437</v>
       </c>
       <c r="S12" t="n">
-        <v>9.5816</v>
+        <v>9.855</v>
       </c>
       <c r="T12" t="n">
-        <v>8.555800000000001</v>
+        <v>8.8292</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0257</v>
+        <v>1.0259</v>
       </c>
       <c r="V12" t="n">
         <v>-0.002700000000000258</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.4436</v>
+        <v>12.9549</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4429</v>
+        <v>13.4222</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9992</v>
+        <v>-0.4673</v>
       </c>
       <c r="G13" t="n">
         <v>10.2691</v>
@@ -1468,13 +1468,13 @@
         <v>1.8529</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.881</v>
+        <v>-1.3698</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2584</v>
+        <v>-0.2791</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6226</v>
+        <v>-1.0906</v>
       </c>
       <c r="V13" t="n">
         <v>2.2027</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4017</v>
+        <v>1.7482</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6106</v>
+        <v>3.9251</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.2089</v>
+        <v>-2.1768</v>
       </c>
       <c r="G15" t="n">
         <v>2.2456</v>
@@ -1624,13 +1624,13 @@
         <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8827</v>
+        <v>-1.5361</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6454</v>
+        <v>-0.0401</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.5281</v>
+        <v>-1.496</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6289</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0667</v>
+        <v>-0.1497</v>
       </c>
       <c r="E16" t="n">
-        <v>0.148</v>
+        <v>0.05</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2147</v>
+        <v>-0.1997</v>
       </c>
       <c r="G16" t="n">
         <v>1.3346</v>
@@ -1702,13 +1702,13 @@
         <v>2.2234</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.531</v>
+        <v>-0.614</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1567</v>
+        <v>0.0588</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6877</v>
+        <v>-0.6728</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3144</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. KALLE</t>
+          <t>S. GALIANO AVILA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4903</v>
+        <v>-0.6632</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5092</v>
+        <v>-0.0454</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0189</v>
+        <v>-0.6178</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0711</v>
+        <v>-0.2743</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.131</v>
+        <v>-0.2866</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0599</v>
+        <v>0.0123</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5054999999999999</v>
+        <v>0.9818</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5884</v>
+        <v>0.8159</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0829</v>
+        <v>0.1659</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5656</v>
+        <v>-1.2561</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5426</v>
+        <v>-1.1026</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.023</v>
+        <v>-0.1536</v>
       </c>
       <c r="P17" t="n">
         <v>0.3706</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3706</v>
+        <v>1.297</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4198</v>
+        <v>-0.1306</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0037</v>
+        <v>-0.1007</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4161</v>
+        <v>-0.0299</v>
       </c>
       <c r="V17" t="n">
-        <v>0.63</v>
+        <v>-0.6289</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.63</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. CISSE</t>
+          <t>S. KALLE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1322</v>
+        <v>-0.76</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2276</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0954</v>
+        <v>-0.055</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2634</v>
+        <v>-1.0711</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0946</v>
+        <v>-1.131</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.358</v>
+        <v>0.0599</v>
       </c>
       <c r="J18" t="n">
-        <v>0.041</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5066000000000001</v>
+        <v>-0.5884</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4656</v>
+        <v>0.0829</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3044</v>
+        <v>-0.5656</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.412</v>
+        <v>-0.5426</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1076</v>
+        <v>-0.023</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9264</v>
+        <v>0.3706</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9264</v>
+        <v>0.3706</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3721</v>
+        <v>-0.6895</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2699</v>
+        <v>-0.1996</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1022</v>
+        <v>-0.49</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3144</v>
+        <v>0.63</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6289</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. GALIANO AVILA</t>
+          <t>S. CISSE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.284</v>
+        <v>-1.4266</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4371</v>
+        <v>-1.4235</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8469</v>
+        <v>-0.0031</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2743</v>
+        <v>-0.2634</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2866</v>
+        <v>0.0946</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0123</v>
+        <v>-0.358</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9818</v>
+        <v>0.041</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8159</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1659</v>
+        <v>-0.4656</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2561</v>
+        <v>-0.3044</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1026</v>
+        <v>-0.412</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1536</v>
+        <v>0.1076</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3706</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>1.297</v>
+        <v>0.9264</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7513</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4924</v>
+        <v>0.074</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2589</v>
+        <v>0.0037</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6289</v>
+        <v>-0.3144</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X19" t="n">
         <v>-0.6289</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3929</v>
+        <v>-2.1638</v>
       </c>
       <c r="E20" t="n">
         <v>-0.5335</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8593</v>
+        <v>-1.6303</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9198</v>
@@ -2014,13 +2014,13 @@
         <v>1.297</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5472</v>
+        <v>-1.3182</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1131</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.4341</v>
+        <v>-1.205</v>
       </c>
       <c r="V20" t="n">
         <v>0.63</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.685</v>
+        <v>-3.0612</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5507</v>
+        <v>-1.0404</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1343</v>
+        <v>-2.0209</v>
       </c>
       <c r="G21" t="n">
         <v>0.2166</v>
@@ -2092,13 +2092,13 @@
         <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4019</v>
+        <v>-0.7781</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3756</v>
+        <v>-0.1141</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7775</v>
+        <v>-0.6641</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5733</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5453</v>
+        <v>-3.3002</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0062</v>
+        <v>-2.8104</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.539</v>
+        <v>-0.4898</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7046</v>
@@ -2170,13 +2170,13 @@
         <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8412</v>
+        <v>-1.5961</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4377</v>
+        <v>-0.2419</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4035</v>
+        <v>-1.3542</v>
       </c>
       <c r="V22" t="n">
         <v>0.63</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1794</v>
+        <v>-4.8032</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0526</v>
+        <v>-4.9547</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1268</v>
+        <v>0.1515</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1109</v>
@@ -2248,13 +2248,13 @@
         <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6974</v>
+        <v>-0.3211</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1679</v>
+        <v>-0.0699</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5295</v>
+        <v>-0.2512</v>
       </c>
       <c r="V23" t="n">
         <v>-0.63</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4201999999999995</v>
+        <v>0.8855000000000004</v>
       </c>
       <c r="E24" t="n">
-        <v>8.394899999999998</v>
+        <v>8.394600000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.814799999999998</v>
+        <v>-7.5092</v>
       </c>
       <c r="G24" t="n">
         <v>8.232099999999999</v>
@@ -2317,7 +2317,7 @@
         <v>4.993</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9265999999999995</v>
+        <v>0.9266</v>
       </c>
       <c r="Q24" t="n">
         <v>-12.0437</v>
@@ -2326,13 +2326,13 @@
         <v>12.9701</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.5814</v>
+        <v>-8.2758</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0256</v>
+        <v>-1.0257</v>
       </c>
       <c r="U24" t="n">
-        <v>-8.5558</v>
+        <v>-7.250100000000001</v>
       </c>
       <c r="V24" t="n">
         <v>0.002800000000000136</v>
